--- a/EIT_2/Labor2/Messprojekt1/Verluste.xlsx
+++ b/EIT_2/Labor2/Messprojekt1/Verluste.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mathias Lampert\Documents\Mathias Schule_Studium\FH\ELITE-Semester\EIT_2\Labor2\Messprojekt1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85008104-DAD2-4458-BFE7-ECE0EF119A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2C3BED-62D4-4AF8-8604-8B64EEBD2573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{FA2FF084-40D9-4D14-954E-A813EBC98D06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FA2FF084-40D9-4D14-954E-A813EBC98D06}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
   <si>
     <t>Infineon</t>
   </si>
@@ -70,12 +70,45 @@
   <si>
     <t>40V, 20R, 1Hz</t>
   </si>
+  <si>
+    <t>Reale Verluste</t>
+  </si>
+  <si>
+    <t>Simulative Verluste</t>
+  </si>
+  <si>
+    <t>Verlustfaktor Vishay</t>
+  </si>
+  <si>
+    <t>Verlustfaktor Nexperia</t>
+  </si>
+  <si>
+    <t>Verlustfaktor Infineon</t>
+  </si>
+  <si>
+    <t>Infineon Re</t>
+  </si>
+  <si>
+    <t>Nexperia Re</t>
+  </si>
+  <si>
+    <t>Vishay Re</t>
+  </si>
+  <si>
+    <t>Infineon Sim</t>
+  </si>
+  <si>
+    <t>Nexperia Sim</t>
+  </si>
+  <si>
+    <t>Vishay Sim</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,16 +116,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -100,11 +161,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -112,14 +193,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="27">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -239,7 +389,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="de-AT"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -255,7 +405,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Tabelle1!$B$2</c:f>
+              <c:f>Tabelle1!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -279,7 +429,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tabelle1!$A$3:$A$7</c:f>
+              <c:f>Tabelle1!$A$4:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -302,7 +452,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$B$3:$B$7</c:f>
+              <c:f>Tabelle1!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -332,7 +482,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Tabelle1!$C$2</c:f>
+              <c:f>Tabelle1!$C$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -356,7 +506,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tabelle1!$A$3:$A$7</c:f>
+              <c:f>Tabelle1!$A$4:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -379,7 +529,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$C$3:$C$7</c:f>
+              <c:f>Tabelle1!$C$4:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -412,7 +562,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Tabelle1!$D$2</c:f>
+              <c:f>Tabelle1!$D$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -436,7 +586,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Tabelle1!$A$3:$A$7</c:f>
+              <c:f>Tabelle1!$A$4:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -459,7 +609,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$D$3:$D$7</c:f>
+              <c:f>Tabelle1!$D$4:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -564,7 +714,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="de-DE"/>
+              <a:endParaRPr lang="de-AT"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -689,7 +839,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="de-DE"/>
+              <a:endParaRPr lang="de-AT"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -874,7 +1024,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="de-AT"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -890,7 +1040,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Tabelle1!$G$2</c:f>
+              <c:f>Tabelle1!$G$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -911,7 +1061,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Tabelle1!$F$3:$F$7</c:f>
+              <c:f>Tabelle1!$F$4:$F$8</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -934,10 +1084,22 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$G$3:$G$7</c:f>
+              <c:f>Tabelle1!$G$4:$G$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.7948300000000001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -952,7 +1114,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Tabelle1!$H$2</c:f>
+              <c:f>Tabelle1!$H$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -973,7 +1135,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Tabelle1!$F$3:$F$7</c:f>
+              <c:f>Tabelle1!$F$4:$F$8</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -996,10 +1158,25 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$H$3:$H$7</c:f>
+              <c:f>Tabelle1!$H$4:$H$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.8071600000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.01174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1014,7 +1191,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Tabelle1!$I$2</c:f>
+              <c:f>Tabelle1!$I$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1035,7 +1212,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Tabelle1!$F$3:$F$7</c:f>
+              <c:f>Tabelle1!$F$4:$F$8</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1058,10 +1235,25 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$I$3:$I$7</c:f>
+              <c:f>Tabelle1!$I$4:$I$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.31819</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.86782</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1274,6 +1466,1259 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-AT"/>
+              <a:t>Dynamischen</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-AT" baseline="0"/>
+              <a:t> Verluste Mosfet - Simulation</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-AT"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-AT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$B$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Infineon</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$A$38:$A$42</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40V, 20R, 1Hz</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$B$38:$B$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.21E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1980000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4430000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9260000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.0200000000000001E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5A7C-4BD9-BFBB-E5B1776376BF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$C$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Nexperia</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$A$38:$A$42</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40V, 20R, 1Hz</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$C$38:$C$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.6600000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.081E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9982000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.8746E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.6834E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5A7C-4BD9-BFBB-E5B1776376BF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$D$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Vishay</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$A$38:$A$42</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40V, 20R, 1Hz</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$D$38:$D$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.1980000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.395E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.6540000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3043000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.7035999999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5A7C-4BD9-BFBB-E5B1776376BF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="228253135"/>
+        <c:axId val="228253615"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="228253135"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="228253615"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="228253615"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="228253135"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-AT"/>
+              <a:t>Dynamische</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-AT" baseline="0"/>
+              <a:t> Verluste im direkten Vergleich</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-AT"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$B$72</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Infineon Re</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$A$73:$A$77</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40V, 20R, 1Hz</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$B$73:$B$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.0200000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.917E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5010999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.113993</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F52E-46FE-9922-0DE2306D4915}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$C$72</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Infineon Sim</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$A$73:$A$77</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40V, 20R, 1Hz</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$C$73:$C$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.21E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1980000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4430000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9260000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.0200000000000001E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F52E-46FE-9922-0DE2306D4915}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$D$72</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Vishay Re</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$A$73:$A$77</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40V, 20R, 1Hz</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$D$73:$D$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.196E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.0362000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.7568000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11867999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.182363</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-F52E-46FE-9922-0DE2306D4915}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$E$72</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Vishay Sim</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$A$73:$A$77</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40V, 20R, 1Hz</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$E$73:$E$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.1980000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.395E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.6540000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3043000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.7035999999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-F52E-46FE-9922-0DE2306D4915}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$F$72</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Nexperia Re</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$A$73:$A$77</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40V, 20R, 1Hz</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$F$73:$F$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.627E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9397000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.1481999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11521199999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.155141</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-F52E-46FE-9922-0DE2306D4915}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$G$72</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Nexperia Sim</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$A$73:$A$77</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35V, 20R, 1Hz</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40V, 20R, 1Hz</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$G$73:$G$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.6600000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.081E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9982000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.8746E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.6834E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-F52E-46FE-9922-0DE2306D4915}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="164463855"/>
+        <c:axId val="164467215"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="164463855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="164467215"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="164467215"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="164463855"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1354,6 +2799,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -1858,6 +3383,1012 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2366,14 +4897,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>184148</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>4846</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1445846</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>14652</xdr:rowOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>22116</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2402,14 +4933,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>12211</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>184149</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>4847</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>1436077</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>175845</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>183308</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2434,30 +4965,131 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>159878</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>7470</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>14949</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Diagramm 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85060E2F-B2A2-E473-2F68-F8F192CCA3E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1437998</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>138</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>8281</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>57978</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Diagramm 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE901AE6-4EA7-36B8-5173-E85FFAE9F202}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F4F71BC1-3520-4F56-98C4-30AFBC3FEF5C}" name="Tabelle2" displayName="Tabelle2" ref="A2:D7" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A2:D7" xr:uid="{F4F71BC1-3520-4F56-98C4-30AFBC3FEF5C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F4F71BC1-3520-4F56-98C4-30AFBC3FEF5C}" name="Tabelle2" displayName="Tabelle2" ref="A3:D8" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+  <autoFilter ref="A3:D8" xr:uid="{F4F71BC1-3520-4F56-98C4-30AFBC3FEF5C}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8E8FC6A2-0530-4186-9AE6-DA6B2E8D4AB8}" name="Rahmenbedingung" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{71743B05-4A07-4828-8864-D472F4E65258}" name="Infineon" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{7E6A8A99-42A0-4D32-9521-8C83F480D20B}" name="Nexperia" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{69A55A23-33F9-4CE6-928B-212B6FB74B02}" name="Vishay" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{8E8FC6A2-0530-4186-9AE6-DA6B2E8D4AB8}" name="Rahmenbedingung" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{71743B05-4A07-4828-8864-D472F4E65258}" name="Infineon" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{7E6A8A99-42A0-4D32-9521-8C83F480D20B}" name="Nexperia" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{69A55A23-33F9-4CE6-928B-212B6FB74B02}" name="Vishay" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C058E90F-3BB3-435D-8D8C-EFF361CA1E0C}" name="Tabelle25" displayName="Tabelle25" ref="F2:I7" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="F2:I7" xr:uid="{C058E90F-3BB3-435D-8D8C-EFF361CA1E0C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C058E90F-3BB3-435D-8D8C-EFF361CA1E0C}" name="Tabelle25" displayName="Tabelle25" ref="F3:I8" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="F3:I8" xr:uid="{C058E90F-3BB3-435D-8D8C-EFF361CA1E0C}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{095DD20D-CF94-466A-A89B-A38F89D56CB3}" name="Rahmenbedingung" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{B5A75993-2923-4B2C-A637-30F13E56F9C5}" name="Infineon" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{6E079F05-3C0F-4DFD-B5F3-F3B9CA28C5DC}" name="Nexperia" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{815E163F-BB43-47EF-8A2A-E182497A7573}" name="Vishay" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{095DD20D-CF94-466A-A89B-A38F89D56CB3}" name="Rahmenbedingung" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{B5A75993-2923-4B2C-A637-30F13E56F9C5}" name="Infineon" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{6E079F05-3C0F-4DFD-B5F3-F3B9CA28C5DC}" name="Nexperia" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{815E163F-BB43-47EF-8A2A-E182497A7573}" name="Vishay" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F02E2C96-CBAB-4661-8918-A9CEA49F9B34}" name="Tabelle22" displayName="Tabelle22" ref="A37:D42" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="A37:D42" xr:uid="{F02E2C96-CBAB-4661-8918-A9CEA49F9B34}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{21010B20-866A-467F-AB30-855C86AE14D8}" name="Rahmenbedingung" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{F7813164-C427-4327-8FA1-5DCE3632F3E6}" name="Infineon" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{CC4DCC8B-9499-472B-AD42-5A518678F569}" name="Nexperia" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{49EB2F6C-6136-4EE0-9D9A-2CD2E3694CB1}" name="Vishay" dataDxfId="9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{757BC227-1296-407E-B65B-B5D5D649AA6A}" name="Tabelle24" displayName="Tabelle24" ref="A72:G77" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A72:G77" xr:uid="{757BC227-1296-407E-B65B-B5D5D649AA6A}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{4DB1BC95-D74E-420B-8C1E-0F0E0F9E4588}" name="Rahmenbedingung" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{3237381B-6B9A-49A3-821C-25A14DD41E60}" name="Infineon Re" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{C5D7B5C1-3D32-44DD-8BC0-E0A691E823AB}" name="Infineon Sim" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{B146C992-A3A8-4579-A765-1768F4C6EFF5}" name="Vishay Re" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{BAB50A0F-36A4-485B-83CE-07AA792E7B05}" name="Vishay Sim" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{EF80923D-E727-4F74-B73F-D2EF9B2A2BB5}" name="Nexperia Re" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{13568BD9-47CA-4CA0-BDBB-6ED86D8BF87E}" name="Nexperia Sim" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2780,159 +5412,190 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFB6FBC7-9FB0-4652-BEE8-F6A2CBCF3729}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="9" width="20.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="F1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
+    <row r="1" spans="1:9" ht="28.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="F2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2">
-        <v>2.0200000000000001E-3</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1.627E-3</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2.196E-3</v>
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>1.917E-2</v>
+        <v>2.0200000000000001E-3</v>
       </c>
       <c r="C4" s="2">
-        <v>1.9397000000000001E-2</v>
+        <v>1.627E-3</v>
       </c>
       <c r="D4" s="2">
-        <v>2.0362000000000002E-2</v>
+        <v>2.196E-3</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>5.5010999999999997E-2</v>
+        <v>1.917E-2</v>
       </c>
       <c r="C5" s="2">
-        <v>4.1481999999999998E-2</v>
+        <v>1.9397000000000001E-2</v>
       </c>
       <c r="D5" s="2">
-        <v>5.7568000000000001E-2</v>
+        <v>2.0362000000000002E-2</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>0.113993</v>
+        <v>5.5010999999999997E-2</v>
       </c>
       <c r="C6" s="2">
-        <v>0.11521199999999999</v>
+        <v>4.1481999999999998E-2</v>
       </c>
       <c r="D6" s="2">
-        <v>0.11867999999999999</v>
+        <v>5.7568000000000001E-2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.113993</v>
+      </c>
       <c r="C7" s="2">
-        <v>0.155141</v>
+        <v>0.11521199999999999</v>
       </c>
       <c r="D7" s="2">
-        <v>0.182363</v>
+        <v>0.11867999999999999</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="G7" s="2">
+        <v>2.7948300000000001</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2.8071600000000001</v>
+      </c>
+      <c r="I7" s="2">
+        <v>2.31819</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="F8" s="1"/>
+      <c r="C8" s="2">
+        <v>0.155141</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.182363</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="H8" s="2">
+        <v>10.01174</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.86782</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
@@ -3164,16 +5827,574 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
     </row>
+    <row r="35" spans="1:9" ht="28.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="2">
+        <v>1.21E-4</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2.6600000000000001E-4</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1.1980000000000001E-3</v>
+      </c>
+      <c r="F38" s="3">
+        <f>B4/Tabelle22[[#This Row],[Infineon]]</f>
+        <v>16.694214876033058</v>
+      </c>
+      <c r="G38" s="3">
+        <f>C4/Tabelle22[[#This Row],[Nexperia]]</f>
+        <v>6.1165413533834583</v>
+      </c>
+      <c r="H38" s="3">
+        <f>D4/Tabelle22[[#This Row],[Vishay]]</f>
+        <v>1.8330550918196995</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="2">
+        <v>1.1980000000000001E-3</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1.081E-2</v>
+      </c>
+      <c r="D39" s="2">
+        <v>2.395E-3</v>
+      </c>
+      <c r="F39" s="3">
+        <f>B5/Tabelle22[[#This Row],[Infineon]]</f>
+        <v>16.001669449081803</v>
+      </c>
+      <c r="G39" s="3">
+        <f>C5/Tabelle22[[#This Row],[Nexperia]]</f>
+        <v>1.7943570767807586</v>
+      </c>
+      <c r="H39" s="3">
+        <f>D5/Tabelle22[[#This Row],[Vishay]]</f>
+        <v>8.5018789144050118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="2">
+        <v>1.4430000000000001E-3</v>
+      </c>
+      <c r="C40" s="2">
+        <v>2.9982000000000002E-2</v>
+      </c>
+      <c r="D40" s="2">
+        <v>6.6540000000000002E-3</v>
+      </c>
+      <c r="F40" s="3">
+        <f>B6/Tabelle22[[#This Row],[Infineon]]</f>
+        <v>38.122661122661121</v>
+      </c>
+      <c r="G40" s="3">
+        <f>C6/Tabelle22[[#This Row],[Nexperia]]</f>
+        <v>1.3835634714161829</v>
+      </c>
+      <c r="H40" s="3">
+        <f>D6/Tabelle22[[#This Row],[Vishay]]</f>
+        <v>8.6516381124135862</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="2">
+        <v>2.9260000000000002E-3</v>
+      </c>
+      <c r="C41" s="2">
+        <v>5.8746E-2</v>
+      </c>
+      <c r="D41" s="2">
+        <v>1.3043000000000001E-2</v>
+      </c>
+      <c r="F41" s="3">
+        <f>B7/Tabelle22[[#This Row],[Infineon]]</f>
+        <v>38.958646616541351</v>
+      </c>
+      <c r="G41" s="3">
+        <f>C7/Tabelle22[[#This Row],[Nexperia]]</f>
+        <v>1.9611888469002143</v>
+      </c>
+      <c r="H41" s="3">
+        <f>D7/Tabelle22[[#This Row],[Vishay]]</f>
+        <v>9.0991336348999461</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" s="2">
+        <v>4.0200000000000001E-3</v>
+      </c>
+      <c r="C42" s="2">
+        <v>7.6834E-2</v>
+      </c>
+      <c r="D42" s="2">
+        <v>1.7035999999999999E-2</v>
+      </c>
+      <c r="F42" s="3">
+        <f>B8/Tabelle22[[#This Row],[Infineon]]</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <f>C8/Tabelle22[[#This Row],[Nexperia]]</f>
+        <v>2.0191712002498896</v>
+      </c>
+      <c r="H42" s="3">
+        <f>D8/Tabelle22[[#This Row],[Vishay]]</f>
+        <v>10.704566799718243</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B73" s="2">
+        <v>2.0200000000000001E-3</v>
+      </c>
+      <c r="C73" s="2">
+        <v>1.21E-4</v>
+      </c>
+      <c r="D73" s="2">
+        <v>2.196E-3</v>
+      </c>
+      <c r="E73" s="2">
+        <v>1.1980000000000001E-3</v>
+      </c>
+      <c r="F73" s="7">
+        <v>1.627E-3</v>
+      </c>
+      <c r="G73" s="2">
+        <v>2.6600000000000001E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" s="2">
+        <v>1.917E-2</v>
+      </c>
+      <c r="C74" s="2">
+        <v>1.1980000000000001E-3</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2.0362000000000002E-2</v>
+      </c>
+      <c r="E74" s="2">
+        <v>2.395E-3</v>
+      </c>
+      <c r="F74" s="8">
+        <v>1.9397000000000001E-2</v>
+      </c>
+      <c r="G74" s="2">
+        <v>1.081E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" s="2">
+        <v>5.5010999999999997E-2</v>
+      </c>
+      <c r="C75" s="2">
+        <v>1.4430000000000001E-3</v>
+      </c>
+      <c r="D75" s="2">
+        <v>5.7568000000000001E-2</v>
+      </c>
+      <c r="E75" s="2">
+        <v>6.6540000000000002E-3</v>
+      </c>
+      <c r="F75" s="7">
+        <v>4.1481999999999998E-2</v>
+      </c>
+      <c r="G75" s="2">
+        <v>2.9982000000000002E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" s="2">
+        <v>0.113993</v>
+      </c>
+      <c r="C76" s="2">
+        <v>2.9260000000000002E-3</v>
+      </c>
+      <c r="D76" s="2">
+        <v>0.11867999999999999</v>
+      </c>
+      <c r="E76" s="2">
+        <v>1.3043000000000001E-2</v>
+      </c>
+      <c r="F76" s="8">
+        <v>0.11521199999999999</v>
+      </c>
+      <c r="G76" s="2">
+        <v>5.8746E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2">
+        <v>4.0200000000000001E-3</v>
+      </c>
+      <c r="D77" s="2">
+        <v>0.182363</v>
+      </c>
+      <c r="E77" s="2">
+        <v>1.7035999999999999E-2</v>
+      </c>
+      <c r="F77" s="9">
+        <v>0.155141</v>
+      </c>
+      <c r="G77" s="2">
+        <v>7.6834E-2</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:I1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A36:D36"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <tableParts count="2">
-    <tablePart r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <tableParts count="4">
     <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100CEBCCB8115044F4DBDFA9C6C5341E19C" ma:contentTypeVersion="10" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="d3980d2ba98d165541a5d616e10085b5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="b67101b8-d0c5-4ad2-9844-013e072659b3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="84d6a2155c2981996bf803d93dc26a7d" ns3:_="">
+    <xsd:import namespace="b67101b8-d0c5-4ad2-9844-013e072659b3"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b67101b8-d0c5-4ad2-9844-013e072659b3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="13" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="17" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhaltstyp"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="b67101b8-d0c5-4ad2-9844-013e072659b3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EA6CFB6-770E-466C-BCAA-D9861FAC5963}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b67101b8-d0c5-4ad2-9844-013e072659b3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F51CB62-213A-47CC-A51E-1B9BCE505172}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b67101b8-d0c5-4ad2-9844-013e072659b3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D64ECFD4-17EC-4AD2-8AFC-C459C3C34CF6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>